--- a/data/trans_camb/P1801_2016_2023-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P1801_2016_2023-Clase-trans_camb.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>4,66</t>
+          <t>4,69</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3,44</t>
+          <t>4,4</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4,29</t>
+          <t>4,76</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 11,16</t>
+          <t>-1,53; 12,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 10,38</t>
+          <t>-2,56; 11,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 8,88</t>
+          <t>-0,1; 9,38</t>
         </is>
       </c>
     </row>
@@ -594,17 +594,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,95%</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 25,44</t>
+          <t>-2,88; 26,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 19,5</t>
+          <t>-4,1; 21,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 17,64</t>
+          <t>-0,17; 18,81</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>7,5</t>
+          <t>5,67</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-1,53</t>
+          <t>-1,92</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,05</t>
+          <t>1,89</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,09; 14,39</t>
+          <t>-1,67; 12,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,12; 5,91</t>
+          <t>-8,89; 5,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 7,92</t>
+          <t>-2,87; 6,61</t>
         </is>
       </c>
     </row>
@@ -690,17 +690,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-2,64%</t>
+          <t>-3,31%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,09; 31,6</t>
+          <t>-2,8; 27,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-13,2; 10,87</t>
+          <t>-14,28; 9,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 15,82</t>
+          <t>-4,99; 13,19</t>
         </is>
       </c>
     </row>
@@ -740,17 +740,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>16,98</t>
+          <t>-1,52</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-5,92</t>
+          <t>-5,67</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11,99</t>
+          <t>-2,27</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 35,92</t>
+          <t>-7,74; 4,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15,61; 4,08</t>
+          <t>-14,78; 5,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 30,21</t>
+          <t>-7,74; 2,93</t>
         </is>
       </c>
     </row>
@@ -786,17 +786,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>-2,85%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-9,32%</t>
+          <t>-8,94%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>-4,07%</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 72,36</t>
+          <t>-13,73; 8,78</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-22,59; 7,03</t>
+          <t>-21,72; 8,71</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 56,27</t>
+          <t>-13,27; 5,5</t>
         </is>
       </c>
     </row>
@@ -836,17 +836,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2,21</t>
+          <t>1,06</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>12,45</t>
+          <t>4,08</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7,64</t>
+          <t>2,45</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 6,49</t>
+          <t>-3,26; 5,63</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,75; 29,06</t>
+          <t>-0,25; 8,85</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,41; 19,47</t>
+          <t>-0,79; 5,87</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 13,95</t>
+          <t>-6,78; 12,35</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,39; 56,39</t>
+          <t>-0,49; 16,99</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,78; 38,79</t>
+          <t>-1,48; 12,07</t>
         </is>
       </c>
     </row>
@@ -932,17 +932,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2,39</t>
+          <t>-1,44</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-3,97</t>
+          <t>1,85</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-0,69</t>
+          <t>1,03</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 9,34</t>
+          <t>-7,43; 4,67</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-16,97; 3,36</t>
+          <t>-2,64; 6,73</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-10,08; 4,22</t>
+          <t>-3,1; 4,61</t>
         </is>
       </c>
     </row>
@@ -978,17 +978,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>-3,2%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-7,16%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-1,37%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -1001,24 +1001,24 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 22,02</t>
+          <t>-15,7; 10,87</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-30,09; 6,06</t>
+          <t>-4,56; 13,04</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-19,53; 8,48</t>
+          <t>-5,86; 9,46</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1028,17 +1028,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>-2,08</t>
+          <t>-4,11</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>-10,63</t>
+          <t>-11,45</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-9,65</t>
+          <t>-10,18</t>
         </is>
       </c>
     </row>
@@ -1051,17 +1051,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-11,05; 9,62</t>
+          <t>-12,32; 5,89</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-15,29; -5,76</t>
+          <t>-16,13; -7,2</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-14,01; -5,22</t>
+          <t>-14,29; -5,7</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>-8,75%</t>
+          <t>-17,33%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>-18,08%</t>
+          <t>-19,46%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-18,75%</t>
+          <t>-19,79%</t>
         </is>
       </c>
     </row>
@@ -1097,17 +1097,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-43,34; 50,34</t>
+          <t>-47,38; 28,81</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-24,91; -9,93</t>
+          <t>-26,44; -12,69</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-26,2; -10,53</t>
+          <t>-27,01; -11,69</t>
         </is>
       </c>
     </row>
@@ -1124,17 +1124,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>6,69</t>
+          <t>1,6</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>-0,07</t>
+          <t>-1,28</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3,25</t>
+          <t>0,15</t>
         </is>
       </c>
     </row>
@@ -1147,17 +1147,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,92; 18,4</t>
+          <t>-0,73; 4,6</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 7,34</t>
+          <t>-3,45; 0,99</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 9,18</t>
+          <t>-1,4; 1,97</t>
         </is>
       </c>
     </row>
@@ -1170,17 +1170,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>-0,13%</t>
+          <t>-2,25%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>0,29%</t>
         </is>
       </c>
     </row>
@@ -1193,17 +1193,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>4,01; 40,65</t>
+          <t>-1,55; 10,14</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 12,74</t>
+          <t>-5,87; 1,79</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 17,99</t>
+          <t>-2,64; 3,88</t>
         </is>
       </c>
     </row>
